--- a/Stock_OneClick/history/scan_result_20260601_135414.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_135414.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -664,24 +664,6 @@
       <c r="J3" t="n">
         <v>185.67</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-01; 相对D0=2.30%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -733,24 +715,6 @@
       <c r="J4" t="n">
         <v>136.62</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-01; 相对D0=-3.26%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -802,27 +766,15 @@
       <c r="J5" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -871,24 +823,12 @@
       <c r="J6" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -940,24 +880,12 @@
       <c r="J7" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1009,24 +937,12 @@
       <c r="J8" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-01; 相对D0=-4.24%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1078,24 +994,6 @@
       <c r="J9" t="n">
         <v>323.39</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-01; 相对D0=-0.16%; 本次触发=2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1147,24 +1045,12 @@
       <c r="J10" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-01; 相对D0=6.26%; 本次触发=2026-06-01(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-01</t>
@@ -1216,24 +1102,6 @@
       <c r="J11" t="n">
         <v>185.67</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1285,24 +1153,6 @@
       <c r="J12" t="n">
         <v>14.7</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1354,24 +1204,12 @@
       <c r="J13" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1423,24 +1261,6 @@
       <c r="J14" t="n">
         <v>320.41</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1492,24 +1312,6 @@
       <c r="J15" t="n">
         <v>185.83</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1561,24 +1363,6 @@
       <c r="J16" t="n">
         <v>136.62</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1630,24 +1414,6 @@
       <c r="J17" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -1699,24 +1465,6 @@
       <c r="J18" t="n">
         <v>27.15</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1768,24 +1516,6 @@
       <c r="J19" t="n">
         <v>50.55</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1837,27 +1567,15 @@
       <c r="J20" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -1906,24 +1624,6 @@
       <c r="J21" t="n">
         <v>905</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -1975,24 +1675,6 @@
       <c r="J22" t="n">
         <v>11.02</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2044,24 +1726,6 @@
       <c r="J23" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2113,24 +1777,12 @@
       <c r="J24" s="5" t="n">
         <v>224.36</v>
       </c>
-      <c r="K24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2182,24 +1834,12 @@
       <c r="J25" s="5" t="n">
         <v>66.89</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2251,24 +1891,6 @@
       <c r="J26" t="n">
         <v>58.92</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2320,24 +1942,6 @@
       <c r="J27" t="n">
         <v>13.89</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2389,24 +1993,6 @@
       <c r="J28" t="n">
         <v>15.58</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2458,24 +2044,12 @@
       <c r="J29" s="5" t="n">
         <v>17.62</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2527,24 +2101,6 @@
       <c r="J30" t="n">
         <v>323.39</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(预警买入)</t>
@@ -2596,24 +2152,6 @@
       <c r="J31" t="n">
         <v>155.71</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 预警买入)</t>
@@ -2665,24 +2203,12 @@
       <c r="J32" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-01; 相对D0=-7.16%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2734,24 +2260,12 @@
       <c r="J33" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-01; 相对D0=-2.56%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -2803,24 +2317,12 @@
       <c r="J34" s="5" t="n">
         <v>54.5</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-01; 相对D0=17.13%</t>
@@ -2872,24 +2374,6 @@
       <c r="J35" t="n">
         <v>16.62</v>
       </c>
-      <c r="K35" t="n">
-        <v/>
-      </c>
-      <c r="L35" t="n">
-        <v/>
-      </c>
-      <c r="M35" t="n">
-        <v/>
-      </c>
-      <c r="N35" t="n">
-        <v/>
-      </c>
-      <c r="O35" t="n">
-        <v/>
-      </c>
-      <c r="P35" t="n">
-        <v/>
-      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-01; 相对D0=3.10%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2941,24 +2425,12 @@
       <c r="J36" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-01; 相对D0=16.40%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3010,24 +2482,12 @@
       <c r="J37" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-01; 相对D0=-1.10%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3079,24 +2539,6 @@
       <c r="J38" t="n">
         <v>400.08</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-01; 相对D0=2.23%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3148,24 +2590,6 @@
       <c r="J39" t="n">
         <v>950.54</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-01; 相对D0=-8.49%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3217,24 +2641,12 @@
       <c r="J40" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-01; 相对D0=23.84%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -3286,24 +2698,6 @@
       <c r="J41" t="n">
         <v>23.33</v>
       </c>
-      <c r="K41" t="n">
-        <v/>
-      </c>
-      <c r="L41" t="n">
-        <v/>
-      </c>
-      <c r="M41" t="n">
-        <v/>
-      </c>
-      <c r="N41" t="n">
-        <v/>
-      </c>
-      <c r="O41" t="n">
-        <v/>
-      </c>
-      <c r="P41" t="n">
-        <v/>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3355,24 +2749,6 @@
       <c r="J42" t="n">
         <v>251.49</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-01; 相对D0=8.40%</t>
@@ -3424,24 +2800,6 @@
       <c r="J43" t="n">
         <v>145.02</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-01; 相对D0=11.13%</t>
@@ -3493,24 +2851,12 @@
       <c r="J44" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-01; 相对D0=-2.49%; 历史重复2次; 重复日期=2026-05-26, 2026-05-27</t>
@@ -3562,24 +2908,12 @@
       <c r="J45" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3631,24 +2965,12 @@
       <c r="J46" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-01; 相对D0=-2.38%</t>
@@ -3700,24 +3022,12 @@
       <c r="J47" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-01; 相对D0=4.38%; 历史重复2次; 重复日期=2026-05-26, 2026-05-29</t>
@@ -3769,24 +3079,6 @@
       <c r="J48" t="n">
         <v>459.97</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-01; 相对D0=9.00%</t>
@@ -3838,24 +3130,6 @@
       <c r="J49" t="n">
         <v>91.22</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-01; 相对D0=5.47%</t>
@@ -3907,24 +3181,12 @@
       <c r="J50" s="5" t="n">
         <v>188.39</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-01; 相对D0=-7.82%</t>
@@ -3976,24 +3238,12 @@
       <c r="J51" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-01; 相对D0=-6.66%</t>
@@ -4045,24 +3295,12 @@
       <c r="J52" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-01; 相对D0=4.09%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4114,24 +3352,6 @@
       <c r="J53" t="n">
         <v>124.82</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-01; 相对D0=17.88%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4183,24 +3403,12 @@
       <c r="J54" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-01; 相对D0=-3.78%</t>
@@ -4252,24 +3460,6 @@
       <c r="J55" t="n">
         <v>400.08</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-01; 相对D0=-0.76%</t>
@@ -4317,24 +3507,12 @@
       <c r="J56" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=88.50; 最新=2026-06-01; 相对D0=-2.06%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4382,24 +3560,12 @@
       <c r="J57" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=158.34; 最新=2026-06-01; 相对D0=-6.73%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4451,24 +3617,6 @@
       <c r="J58" t="n">
         <v>950.54</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-01; 相对D0=-11.20%</t>
@@ -4520,24 +3668,12 @@
       <c r="J59" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-01; 相对D0=-3.22%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4589,24 +3725,12 @@
       <c r="J60" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-01; 相对D0=3.08%</t>
@@ -4658,24 +3782,12 @@
       <c r="J61" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-01; 相对D0=-1.94%</t>
@@ -4727,24 +3839,6 @@
       <c r="J62" t="n">
         <v>23.33</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%</t>
@@ -4796,24 +3890,12 @@
       <c r="J63" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-01; 相对D0=-6.73%</t>
@@ -4865,24 +3947,6 @@
       <c r="J64" t="n">
         <v>108.96</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
-      <c r="L64" t="n">
-        <v/>
-      </c>
-      <c r="M64" t="n">
-        <v/>
-      </c>
-      <c r="N64" t="n">
-        <v/>
-      </c>
-      <c r="O64" t="n">
-        <v/>
-      </c>
-      <c r="P64" t="n">
-        <v/>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-01; 相对D0=1.89%</t>
@@ -4934,24 +3998,12 @@
       <c r="J65" s="5" t="n">
         <v>12.89</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%</t>
@@ -5003,24 +4055,6 @@
       <c r="J66" t="n">
         <v>83.78</v>
       </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
-      <c r="L66" t="n">
-        <v/>
-      </c>
-      <c r="M66" t="n">
-        <v/>
-      </c>
-      <c r="N66" t="n">
-        <v/>
-      </c>
-      <c r="O66" t="n">
-        <v/>
-      </c>
-      <c r="P66" t="n">
-        <v/>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-01; 相对D0=-1.02%</t>
@@ -5072,24 +4106,12 @@
       <c r="J67" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-01; 相对D0=0.59%</t>
@@ -5141,24 +4163,6 @@
       <c r="J68" t="n">
         <v>185.67</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-01; 相对D0=3.25%</t>
@@ -5210,24 +4214,12 @@
       <c r="J69" s="5" t="n">
         <v>261.26</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-01; 相对D0=-3.90%</t>
@@ -5275,24 +4267,12 @@
       <c r="J70" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-01; 相对D0=0.18%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -5344,24 +4324,6 @@
       <c r="J71" t="n">
         <v>16.62</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-01; 相对D0=0.97%</t>
@@ -5409,24 +4371,12 @@
       <c r="J72" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>D0=41.35; 最新=2026-06-01; 相对D0=-6.19%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -5478,24 +4428,12 @@
       <c r="J73" s="5" t="n">
         <v>135.86</v>
       </c>
-      <c r="K73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
       <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-01; 相对D0=33.04%</t>
@@ -5547,24 +4485,12 @@
       <c r="J74" s="5" t="n">
         <v>255.71</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-01; 相对D0=-4.19%</t>
@@ -5616,24 +4542,6 @@
       <c r="J75" t="n">
         <v>248.15</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-01; 相对D0=29.95%</t>
@@ -5685,24 +4593,12 @@
       <c r="J76" s="5" t="n">
         <v>115.95</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%</t>
@@ -5754,24 +4650,6 @@
       <c r="J77" t="n">
         <v>273.51</v>
       </c>
-      <c r="K77" t="n">
-        <v/>
-      </c>
-      <c r="L77" t="n">
-        <v/>
-      </c>
-      <c r="M77" t="n">
-        <v/>
-      </c>
-      <c r="N77" t="n">
-        <v/>
-      </c>
-      <c r="O77" t="n">
-        <v/>
-      </c>
-      <c r="P77" t="n">
-        <v/>
-      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-01; 相对D0=-5.69%</t>
@@ -5819,24 +4697,12 @@
       <c r="J78" s="5" t="n">
         <v>91.03</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-01; 相对D0=-0.07%</t>
@@ -5888,24 +4754,12 @@
       <c r="J79" s="5" t="n">
         <v>112.59</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-01; 相对D0=1.77%</t>
@@ -5957,24 +4811,12 @@
       <c r="J80" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O80" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P80" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="5" t="n"/>
+      <c r="M80" s="5" t="n"/>
+      <c r="N80" s="5" t="n"/>
+      <c r="O80" s="5" t="n"/>
+      <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-01; 相对D0=18.98%</t>
@@ -6026,24 +4868,6 @@
       <c r="J81" t="n">
         <v>782.17</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -6095,24 +4919,6 @@
       <c r="J82" t="n">
         <v>124.82</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-01; 相对D0=16.81%</t>
@@ -6164,24 +4970,6 @@
       <c r="J83" t="n">
         <v>64.61</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-01; 相对D0=-4.11%</t>
@@ -6229,24 +5017,12 @@
       <c r="J84" s="5" t="n">
         <v>1050.77</v>
       </c>
-      <c r="K84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O84" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P84" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="n"/>
+      <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
+      <c r="P84" s="5" t="n"/>
       <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-01; 相对D0=-1.75%</t>
@@ -6298,24 +5074,6 @@
       <c r="J85" t="n">
         <v>147.14</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-01; 相对D0=13.45%</t>
@@ -6363,24 +5121,12 @@
       <c r="J86" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=87.18; 最新=2026-06-01; 相对D0=-0.57%</t>
@@ -6428,24 +5174,12 @@
       <c r="J87" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>D0=150.11; 最新=2026-06-01; 相对D0=-1.61%</t>
@@ -6497,24 +5231,12 @@
       <c r="J88" s="5" t="n">
         <v>376.37</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-01; 相对D0=-3.53%</t>
@@ -6566,24 +5288,12 @@
       <c r="J89" s="5" t="n">
         <v>107.7</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-01; 相对D0=12.56%</t>
@@ -6635,24 +5345,12 @@
       <c r="J90" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-01; 相对D0=1.91%</t>
@@ -6704,24 +5402,12 @@
       <c r="J91" s="5" t="n">
         <v>403.88</v>
       </c>
-      <c r="K91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-01; 相对D0=24.01%</t>
@@ -6773,24 +5459,12 @@
       <c r="J92" s="5" t="n">
         <v>460.52</v>
       </c>
-      <c r="K92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O92" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-01; 相对D0=7.85%</t>
@@ -6842,24 +5516,6 @@
       <c r="J93" t="n">
         <v>264.51</v>
       </c>
-      <c r="K93" t="n">
-        <v/>
-      </c>
-      <c r="L93" t="n">
-        <v/>
-      </c>
-      <c r="M93" t="n">
-        <v/>
-      </c>
-      <c r="N93" t="n">
-        <v/>
-      </c>
-      <c r="O93" t="n">
-        <v/>
-      </c>
-      <c r="P93" t="n">
-        <v/>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-01; 相对D0=16.86%</t>
@@ -6911,24 +5567,6 @@
       <c r="J94" t="n">
         <v>139.79</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-01; 相对D0=47.58%</t>
@@ -6980,24 +5618,6 @@
       <c r="J95" t="n">
         <v>300.48</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-01; 相对D0=16.57%</t>
@@ -7049,24 +5669,12 @@
       <c r="J96" s="5" t="n">
         <v>160.65</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-01; 相对D0=12.08%</t>
@@ -7118,24 +5726,12 @@
       <c r="J97" s="5" t="n">
         <v>274.03</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%</t>
@@ -7187,24 +5783,12 @@
       <c r="J98" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%</t>
@@ -7256,24 +5840,12 @@
       <c r="J99" s="5" t="n">
         <v>265.7</v>
       </c>
-      <c r="K99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O99" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P99" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="5" t="n"/>
+      <c r="M99" s="5" t="n"/>
+      <c r="N99" s="5" t="n"/>
+      <c r="O99" s="5" t="n"/>
+      <c r="P99" s="5" t="n"/>
       <c r="Q99" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-01; 相对D0=-7.66%</t>
@@ -7325,24 +5897,12 @@
       <c r="J100" s="5" t="n">
         <v>209.6</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-01; 相对D0=9.68%</t>
@@ -7394,24 +5954,12 @@
       <c r="J101" s="5" t="n">
         <v>47.59</v>
       </c>
-      <c r="K101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O101" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P101" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
       <c r="Q101" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-01; 相对D0=-1.71%</t>
@@ -7459,24 +6007,12 @@
       <c r="J102" s="5" t="n">
         <v>86.68000000000001</v>
       </c>
-      <c r="K102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O102" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P102" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
       <c r="Q102" s="5" t="inlineStr">
         <is>
           <t>D0=89.49; 最新=2026-06-01; 相对D0=-3.14%</t>
@@ -7524,24 +6060,12 @@
       <c r="J103" s="5" t="n">
         <v>147.69</v>
       </c>
-      <c r="K103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="5" t="n"/>
+      <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
       <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>D0=163.35; 最新=2026-06-01; 相对D0=-9.59%</t>
@@ -7593,24 +6117,12 @@
       <c r="J104" s="5" t="n">
         <v>13.59</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-01; 相对D0=-1.31%</t>
@@ -7662,24 +6174,6 @@
       <c r="J105" t="n">
         <v>115.58</v>
       </c>
-      <c r="K105" t="n">
-        <v/>
-      </c>
-      <c r="L105" t="n">
-        <v/>
-      </c>
-      <c r="M105" t="n">
-        <v/>
-      </c>
-      <c r="N105" t="n">
-        <v/>
-      </c>
-      <c r="O105" t="n">
-        <v/>
-      </c>
-      <c r="P105" t="n">
-        <v/>
-      </c>
       <c r="Q105" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -7727,24 +6221,12 @@
       <c r="J106" s="5" t="n">
         <v>99.182</v>
       </c>
-      <c r="K106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P106" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
       <c r="Q106" s="5" t="inlineStr">
         <is>
           <t>D0=99.18; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -7792,24 +6274,12 @@
       <c r="J107" s="5" t="n">
         <v>38.79</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=38.79; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -7857,24 +6327,12 @@
       <c r="J108" s="5" t="n">
         <v>16.05</v>
       </c>
-      <c r="K108" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N108" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O108" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P108" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="5" t="n"/>
+      <c r="M108" s="5" t="n"/>
+      <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="n"/>
+      <c r="P108" s="5" t="n"/>
       <c r="Q108" s="5" t="inlineStr">
         <is>
           <t>D0=16.05; 最新=2026-06-01; 相对D0=0.00%</t>
@@ -8111,24 +6569,12 @@
       <c r="J120" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="5" t="n"/>
+      <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
       <c r="Q120" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-01; 相对D0=-4.99%; 本次触发=2026-06-01(正式卖出); 历史重复1次; 重复日期=2026-06-01</t>
@@ -8180,24 +6626,6 @@
       <c r="J121" t="n">
         <v>105.65</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -8249,24 +6677,12 @@
       <c r="J122" s="5" t="n">
         <v>163.09</v>
       </c>
-      <c r="K122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P122" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K122" s="5" t="n"/>
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="5" t="n"/>
+      <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="5" t="n"/>
       <c r="Q122" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -8318,24 +6734,6 @@
       <c r="J123" t="n">
         <v>64.61</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -8387,24 +6785,12 @@
       <c r="J124" s="5" t="n">
         <v>135.73</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -8456,24 +6842,12 @@
       <c r="J125" s="5" t="n">
         <v>600.47</v>
       </c>
-      <c r="K125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P125" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
       <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -8525,24 +6899,12 @@
       <c r="J126" s="5" t="n">
         <v>24.86</v>
       </c>
-      <c r="K126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P126" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K126" s="5" t="n"/>
+      <c r="L126" s="5" t="n"/>
+      <c r="M126" s="5" t="n"/>
+      <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
+      <c r="P126" s="5" t="n"/>
       <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出)</t>
@@ -8594,24 +6956,12 @@
       <c r="J127" s="5" t="n">
         <v>415.88</v>
       </c>
-      <c r="K127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P127" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="5" t="n"/>
+      <c r="M127" s="5" t="n"/>
+      <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
       <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式卖出 | 预警卖出)</t>
@@ -8663,24 +7013,12 @@
       <c r="J128" s="5" t="n">
         <v>39.35</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-01; 相对D0=-5.11%</t>
@@ -8701,7 +7039,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8728,24 +7065,6 @@
       <c r="J129" t="n">
         <v>91.03</v>
       </c>
-      <c r="K129" t="n">
-        <v/>
-      </c>
-      <c r="L129" t="n">
-        <v/>
-      </c>
-      <c r="M129" t="n">
-        <v/>
-      </c>
-      <c r="N129" t="n">
-        <v/>
-      </c>
-      <c r="O129" t="n">
-        <v/>
-      </c>
-      <c r="P129" t="n">
-        <v/>
-      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-01; 相对D0=0.43%</t>
@@ -8797,24 +7116,12 @@
       <c r="J130" s="5" t="n">
         <v>185.83</v>
       </c>
-      <c r="K130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-01; 相对D0=0.61%</t>
@@ -8866,24 +7173,12 @@
       <c r="J131" s="5" t="n">
         <v>136.62</v>
       </c>
-      <c r="K131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="5" t="n"/>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-01; 相对D0=0.31%</t>
@@ -8904,7 +7199,6 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -8931,24 +7225,6 @@
       <c r="J132" t="n">
         <v>38.79</v>
       </c>
-      <c r="K132" t="n">
-        <v/>
-      </c>
-      <c r="L132" t="n">
-        <v/>
-      </c>
-      <c r="M132" t="n">
-        <v/>
-      </c>
-      <c r="N132" t="n">
-        <v/>
-      </c>
-      <c r="O132" t="n">
-        <v/>
-      </c>
-      <c r="P132" t="n">
-        <v/>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>D0=37.61; 最新=2026-06-01; 相对D0=3.14%</t>
@@ -9000,24 +7276,6 @@
       <c r="J133" t="n">
         <v>403.88</v>
       </c>
-      <c r="K133" t="n">
-        <v/>
-      </c>
-      <c r="L133" t="n">
-        <v/>
-      </c>
-      <c r="M133" t="n">
-        <v/>
-      </c>
-      <c r="N133" t="n">
-        <v/>
-      </c>
-      <c r="O133" t="n">
-        <v/>
-      </c>
-      <c r="P133" t="n">
-        <v/>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-01; 相对D0=31.41%</t>
@@ -9069,24 +7327,12 @@
       <c r="J134" s="5" t="n">
         <v>58.92</v>
       </c>
-      <c r="K134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-01; 相对D0=2.54%</t>
@@ -9138,24 +7384,12 @@
       <c r="J135" s="5" t="n">
         <v>13.89</v>
       </c>
-      <c r="K135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="5" t="n"/>
+      <c r="N135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="5" t="n"/>
       <c r="Q135" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-01; 相对D0=4.04%</t>
@@ -9207,24 +7441,12 @@
       <c r="J136" s="5" t="n">
         <v>54.75</v>
       </c>
-      <c r="K136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-01; 相对D0=-3.10%</t>
@@ -9276,24 +7498,6 @@
       <c r="J137" t="n">
         <v>155.71</v>
       </c>
-      <c r="K137" t="n">
-        <v/>
-      </c>
-      <c r="L137" t="n">
-        <v/>
-      </c>
-      <c r="M137" t="n">
-        <v/>
-      </c>
-      <c r="N137" t="n">
-        <v/>
-      </c>
-      <c r="O137" t="n">
-        <v/>
-      </c>
-      <c r="P137" t="n">
-        <v/>
-      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-01; 相对D0=23.18%</t>
@@ -9345,24 +7549,12 @@
       <c r="J138" s="5" t="n">
         <v>109.55</v>
       </c>
-      <c r="K138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K138" s="5" t="n"/>
+      <c r="L138" s="5" t="n"/>
+      <c r="M138" s="5" t="n"/>
+      <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
+      <c r="P138" s="5" t="n"/>
       <c r="Q138" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-01; 相对D0=-5.32%</t>
@@ -9414,24 +7606,6 @@
       <c r="J139" t="n">
         <v>265.7</v>
       </c>
-      <c r="K139" t="n">
-        <v/>
-      </c>
-      <c r="L139" t="n">
-        <v/>
-      </c>
-      <c r="M139" t="n">
-        <v/>
-      </c>
-      <c r="N139" t="n">
-        <v/>
-      </c>
-      <c r="O139" t="n">
-        <v/>
-      </c>
-      <c r="P139" t="n">
-        <v/>
-      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-01; 相对D0=-7.20%</t>
@@ -9483,24 +7657,12 @@
       <c r="J140" s="5" t="n">
         <v>176.7</v>
       </c>
-      <c r="K140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="5" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="5" t="n"/>
+      <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-01; 相对D0=-3.43%</t>
@@ -9552,24 +7714,6 @@
       <c r="J141" t="n">
         <v>492.29</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-01; 相对D0=2.42%</t>
@@ -9621,24 +7765,12 @@
       <c r="J142" s="5" t="n">
         <v>93.62</v>
       </c>
-      <c r="K142" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L142" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N142" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O142" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P142" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K142" s="5" t="n"/>
+      <c r="L142" s="5" t="n"/>
+      <c r="M142" s="5" t="n"/>
+      <c r="N142" s="5" t="n"/>
+      <c r="O142" s="5" t="n"/>
+      <c r="P142" s="5" t="n"/>
       <c r="Q142" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-01; 相对D0=1.40%</t>
@@ -9690,24 +7822,12 @@
       <c r="J143" s="5" t="n">
         <v>72.75</v>
       </c>
-      <c r="K143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P143" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K143" s="5" t="n"/>
+      <c r="L143" s="5" t="n"/>
+      <c r="M143" s="5" t="n"/>
+      <c r="N143" s="5" t="n"/>
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="5" t="n"/>
       <c r="Q143" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-01; 相对D0=4.59%</t>
@@ -9759,24 +7879,6 @@
       <c r="J144" t="n">
         <v>273.51</v>
       </c>
-      <c r="K144" t="n">
-        <v/>
-      </c>
-      <c r="L144" t="n">
-        <v/>
-      </c>
-      <c r="M144" t="n">
-        <v/>
-      </c>
-      <c r="N144" t="n">
-        <v/>
-      </c>
-      <c r="O144" t="n">
-        <v/>
-      </c>
-      <c r="P144" t="n">
-        <v/>
-      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-01; 相对D0=-4.03%</t>
@@ -9828,24 +7930,12 @@
       <c r="J145" s="5" t="n">
         <v>362.9</v>
       </c>
-      <c r="K145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P145" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K145" s="5" t="n"/>
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="5" t="n"/>
+      <c r="N145" s="5" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="5" t="n"/>
       <c r="Q145" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-01; 相对D0=0.40%</t>
@@ -9897,24 +7987,6 @@
       <c r="J146" t="n">
         <v>27.15</v>
       </c>
-      <c r="K146" t="n">
-        <v/>
-      </c>
-      <c r="L146" t="n">
-        <v/>
-      </c>
-      <c r="M146" t="n">
-        <v/>
-      </c>
-      <c r="N146" t="n">
-        <v/>
-      </c>
-      <c r="O146" t="n">
-        <v/>
-      </c>
-      <c r="P146" t="n">
-        <v/>
-      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-01; 相对D0=43.80%</t>
@@ -9966,24 +8038,6 @@
       <c r="J147" t="n">
         <v>109.33</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-01; 相对D0=-4.67%</t>
@@ -10035,24 +8089,12 @@
       <c r="J148" s="5" t="n">
         <v>129.47</v>
       </c>
-      <c r="K148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P148" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K148" s="5" t="n"/>
+      <c r="L148" s="5" t="n"/>
+      <c r="M148" s="5" t="n"/>
+      <c r="N148" s="5" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="5" t="n"/>
       <c r="Q148" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-01; 相对D0=-3.44%</t>
@@ -10104,24 +8146,12 @@
       <c r="J149" s="5" t="n">
         <v>252.53</v>
       </c>
-      <c r="K149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="5" t="n"/>
+      <c r="L149" s="5" t="n"/>
+      <c r="M149" s="5" t="n"/>
+      <c r="N149" s="5" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="5" t="n"/>
       <c r="Q149" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-01; 相对D0=-1.06%</t>
@@ -10218,7 +8248,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10230,7 +8259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10453,7 +8482,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -10734,7 +8763,6 @@
       <c r="M10" s="18" t="n">
         <v>-0.04189</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -10960,9 +8988,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B23" s="21" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -11008,9 +9034,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B24" s="21" t="n"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -11101,10 +9125,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11116,7 +9136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -11652,7 +9672,6 @@
       <c r="K12" s="19" t="n">
         <v>0.16807</v>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11681,7 +9700,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -11694,7 +9712,6 @@
       <c r="K13" s="18" t="n">
         <v>-0.056895</v>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -11769,7 +9786,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -11782,7 +9798,6 @@
       <c r="K15" s="18" t="n">
         <v>-0.04111</v>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -11895,7 +9910,6 @@
       <c r="F18" t="n">
         <v>226.34</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>231.09</v>
       </c>
@@ -11908,7 +9922,6 @@
       <c r="K18" s="19" t="n">
         <v>0.16864</v>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -12244,9 +10257,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="21" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -12286,9 +10297,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="21" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -12328,9 +10337,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="21" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -12370,9 +10377,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="21" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -12470,9 +10475,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12484,7 +10486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -12655,7 +10657,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -13066,9 +11068,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B23" s="21" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -13102,9 +11102,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B24" s="21" t="n"/>
       <c r="C24" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -13138,9 +11136,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B25" s="21" t="n"/>
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -13174,9 +11170,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="21" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -13214,9 +11208,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="21" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -13250,9 +11242,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="21" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -13286,9 +11276,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="21" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -13322,9 +11310,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="21" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -13358,9 +11344,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="21" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -13478,7 +11462,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13490,7 +11473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -13607,7 +11590,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F4" s="12" t="n">
@@ -13767,8 +11750,6 @@
       <c r="F9" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -13887,8 +11868,6 @@
       <c r="F13" t="n">
         <v>14.7</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -13985,8 +11964,6 @@
       <c r="F16" t="n">
         <v>15.58</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -14084,7 +12061,6 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -14484,9 +12460,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -14514,9 +12488,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -14548,9 +12520,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -14578,9 +12548,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -14608,9 +12576,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -14638,9 +12604,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -14668,9 +12632,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -14782,7 +12744,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15180,7 +13141,6 @@
       <c r="V4" t="n">
         <v>315</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.44; 4H分金=38.99</t>
@@ -15538,7 +13498,6 @@
       <c r="V8" t="n">
         <v>274.75</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.87; 4H分金=29.59</t>
@@ -15806,7 +13765,6 @@
       <c r="V11" t="n">
         <v>133.8600006103516</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=133.86; Gann0=69.92; 段涨幅=91.45%</t>
@@ -15894,7 +13852,6 @@
       <c r="V12" t="n">
         <v>178.9100036621094</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=178.91; Gann0=147.57; 段涨幅=21.24%</t>
@@ -15976,8 +13933,6 @@
       <c r="T13" t="b">
         <v>0</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
         <v>94</v>
       </c>
@@ -16068,7 +14023,6 @@
       <c r="V14" t="n">
         <v>68.97000122070312</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-18; 1出价格=68.97; Gann0=61.71; 段涨幅=11.76%</t>
@@ -16156,7 +14110,6 @@
       <c r="V15" t="n">
         <v>73.73999786376953</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.65; 4H分金=39.11</t>
@@ -16244,7 +14197,6 @@
       <c r="V16" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=149.31; Gann0=122.00; 段涨幅=22.39%</t>
@@ -16332,7 +14284,6 @@
       <c r="V17" t="n">
         <v>149.3099975585938</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.17; 4H分金=37.91</t>
@@ -16414,8 +14365,6 @@
       <c r="T18" t="b">
         <v>0</v>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
         <v>86</v>
       </c>
@@ -16596,7 +14545,6 @@
       <c r="V20" t="n">
         <v>409.6499938964844</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.92; 4H分金=50.49</t>
@@ -17082,7 +15030,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -17488,8 +15436,6 @@
       <c r="T30" t="b">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="n">
         <v>91</v>
       </c>
@@ -17580,7 +15526,6 @@
       <c r="V31" t="n">
         <v>11.90999984741211</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.02; 4H分金=49.87</t>
@@ -17668,7 +15613,6 @@
       <c r="V32" t="n">
         <v>643</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=643.00; Gann0=594.81; 段涨幅=8.10%</t>
@@ -17756,7 +15700,6 @@
       <c r="V33" t="n">
         <v>643</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=40.60; 4H分金=32.16</t>
@@ -17844,7 +15787,6 @@
       <c r="V34" t="n">
         <v>24.5</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.29; 4H分金=49.04</t>
@@ -17932,7 +15874,6 @@
       <c r="V35" t="n">
         <v>134.1100006103516</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=45.14; 4H分金=41.50</t>
@@ -18014,8 +15955,6 @@
       <c r="T36" t="b">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="n">
         <v>95</v>
       </c>
@@ -18286,7 +16225,6 @@
       <c r="V39" t="n">
         <v>33.81999969482422</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=33.82; Gann0=17.50; 段涨幅=93.26%</t>
@@ -18644,7 +16582,6 @@
       <c r="V43" t="n">
         <v>56.84000015258789</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.79; 4H分金=45.24</t>
@@ -19002,7 +16939,6 @@
       <c r="V47" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=58.29; 4H分金=52.30</t>
@@ -19090,7 +17026,6 @@
       <c r="V48" t="n">
         <v>86.43000030517578</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.54; 4H分金=45.20</t>
@@ -19178,7 +17113,6 @@
       <c r="V49" t="n">
         <v>394.6300048828125</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.55; 4H分金=50.76</t>
@@ -19266,7 +17200,6 @@
       <c r="V50" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-27; 1出价格=445.60; Gann0=393.63; 段涨幅=13.20%</t>
@@ -19354,7 +17287,6 @@
       <c r="V51" t="n">
         <v>445.6000061035156</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.10; 4H分金=24.03</t>
@@ -19442,7 +17374,6 @@
       <c r="V52" t="n">
         <v>13.93000030517578</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.48; 4H分金=47.96</t>
@@ -19524,8 +17455,6 @@
       <c r="T53" t="b">
         <v>0</v>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="n">
         <v>86</v>
       </c>
@@ -19610,8 +17539,6 @@
       <c r="T54" t="b">
         <v>0</v>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
         <v>91</v>
       </c>
@@ -19702,7 +17629,6 @@
       <c r="V55" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.12; 4H分金=40.44</t>
@@ -19790,7 +17716,6 @@
       <c r="V56" t="n">
         <v>51.58000183105469</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.41; 4H分金=45.41</t>
@@ -20129,7 +18054,6 @@
       <c r="D2" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46170</v>
       </c>
@@ -20178,7 +18102,6 @@
           <t>98 超巨</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -20233,7 +18156,6 @@
       <c r="D4" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -20339,7 +18261,6 @@
       <c r="D6" s="8" t="n">
         <v>46170</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46170</v>
       </c>
@@ -20998,7 +18919,6 @@
       <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="8" t="n">
         <v>46171</v>
       </c>
@@ -21110,7 +19030,6 @@
       <c r="I11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" s="8" t="n">
         <v>46169</v>
       </c>
@@ -21199,7 +19118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21668,7 +19587,6 @@
       <c r="F8" t="n">
         <v>181.49</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>177.62</v>
       </c>
@@ -21984,7 +19902,6 @@
       <c r="F13" t="n">
         <v>16.12</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>15.47</v>
       </c>
@@ -22300,7 +20217,6 @@
       <c r="F18" t="n">
         <v>141.22</v>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>136.2</v>
       </c>
@@ -22364,7 +20280,6 @@
       <c r="F19" t="n">
         <v>426.01</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>433.59</v>
       </c>
@@ -22395,7 +20310,6 @@
       <c r="Q19" s="18" t="n">
         <v>-0.023779</v>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -22488,7 +20402,6 @@
       <c r="F21" t="n">
         <v>232</v>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>240.29</v>
       </c>
@@ -22519,7 +20432,6 @@
       <c r="Q21" s="19" t="n">
         <v>0.084009</v>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22"/>
     <row r="23">
@@ -22717,9 +20629,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="21" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -22809,11 +20719,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22825,7 +20730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -22986,24 +20891,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23055,24 +20948,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23124,24 +21005,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23193,24 +21062,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23262,24 +21119,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23331,24 +21170,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23400,24 +21227,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23469,24 +21284,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23538,24 +21335,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23607,24 +21392,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23676,24 +21449,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23745,24 +21506,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23814,24 +21563,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23883,24 +21614,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -23952,24 +21665,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24021,24 +21716,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24090,24 +21773,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24159,24 +21830,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24228,24 +21881,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24482,24 +22123,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24544,11 +22173,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24560,7 +22184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25041,7 +22665,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -25835,7 +23458,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -25870,7 +23493,6 @@
       <c r="O23" s="19" t="n">
         <v>0.031388</v>
       </c>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -25893,7 +23515,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -25953,7 +23575,6 @@
       <c r="F25" t="n">
         <v>86.48999999999999</v>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>87.83</v>
       </c>
@@ -25978,7 +23599,6 @@
       <c r="O25" s="19" t="n">
         <v>0.054688</v>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -26001,7 +23621,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -26224,9 +23844,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="21" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -26278,9 +23896,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -26332,9 +23948,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="21" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -26386,9 +24000,7 @@
           <t>GDXD</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -26440,9 +24052,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B42" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="21" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -26494,9 +24104,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="21" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -26548,9 +24156,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -26673,8 +24279,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
